--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,971 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125878396</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 26574, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>600853</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6423910</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125878521</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110194</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 26574, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>600490</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6424109</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sparsam på marken.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125878682</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57069</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Frisksjön, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>600420</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6424071</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125878480</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 26574, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600760</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6423958</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125878560</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110404</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 26574, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>600449</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6424110</v>
+      </c>
+      <c r="S7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Talrik - många 100 i ett större område nedanför berget</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125878570</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101394</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 26574, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>600449</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6424110</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sparsam</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125878370</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95927</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 26574, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>600917</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6423833</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125878387</v>
+      </c>
+      <c r="B10" t="n">
+        <v>95927</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 26754, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>600861</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6423915</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125878451</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 26574, Averum, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>600764</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6423946</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125878396</v>
       </c>
       <c r="B3" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110194</v>
+        <v>110201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>125878480</v>
       </c>
       <c r="B6" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110404</v>
+        <v>110411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101394</v>
+        <v>101401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125878396</v>
       </c>
       <c r="B3" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110201</v>
+        <v>110202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>125878480</v>
       </c>
       <c r="B6" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110411</v>
+        <v>110412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101401</v>
+        <v>101402</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95934</v>
+        <v>95935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95934</v>
+        <v>95935</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>125878451</v>
       </c>
       <c r="B11" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110202</v>
+        <v>110204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110412</v>
+        <v>110414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101402</v>
+        <v>101404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95935</v>
+        <v>95937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95935</v>
+        <v>95937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125878396</v>
       </c>
       <c r="B3" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110204</v>
+        <v>110208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>125878480</v>
       </c>
       <c r="B6" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110414</v>
+        <v>110418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101404</v>
+        <v>101408</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110208</v>
+        <v>110209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110418</v>
+        <v>110419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101408</v>
+        <v>101409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125878396</v>
       </c>
       <c r="B3" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110209</v>
+        <v>110211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>125878682</v>
       </c>
       <c r="B5" t="n">
-        <v>57069</v>
+        <v>57070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>125878480</v>
       </c>
       <c r="B6" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110419</v>
+        <v>110421</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101409</v>
+        <v>101411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>125878451</v>
       </c>
       <c r="B11" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125878396</v>
       </c>
       <c r="B3" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110211</v>
+        <v>110213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>125878480</v>
       </c>
       <c r="B6" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110421</v>
+        <v>110423</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101411</v>
+        <v>101413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125878396</v>
       </c>
       <c r="B3" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110213</v>
+        <v>110217</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>125878480</v>
       </c>
       <c r="B6" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110423</v>
+        <v>110427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101413</v>
+        <v>101415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125878396</v>
       </c>
       <c r="B3" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110217</v>
+        <v>110230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>125878682</v>
       </c>
       <c r="B5" t="n">
-        <v>57070</v>
+        <v>57074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>125878480</v>
       </c>
       <c r="B6" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110427</v>
+        <v>110440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101415</v>
+        <v>101419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>125878451</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110230</v>
+        <v>110233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110440</v>
+        <v>110443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101419</v>
+        <v>101422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 26574-2025 artfynd.xlsx
+++ b/artfynd/A 26574-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125878396</v>
       </c>
       <c r="B3" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>125878521</v>
       </c>
       <c r="B4" t="n">
-        <v>110233</v>
+        <v>110242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>125878682</v>
       </c>
       <c r="B5" t="n">
-        <v>57074</v>
+        <v>57075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>125878480</v>
       </c>
       <c r="B6" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125878560</v>
       </c>
       <c r="B7" t="n">
-        <v>110443</v>
+        <v>110452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>125878570</v>
       </c>
       <c r="B8" t="n">
-        <v>101422</v>
+        <v>101431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>125878370</v>
       </c>
       <c r="B9" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>125878387</v>
       </c>
       <c r="B10" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>125878451</v>
       </c>
       <c r="B11" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
